--- a/output/pdf_financials_xlsx/MLO.xlsx
+++ b/output/pdf_financials_xlsx/MLO.xlsx
@@ -1388,19 +1388,19 @@
         <v>0.181357</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.07227</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.005132</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.009891</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.07908</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.33971</v>
       </c>
     </row>
     <row r="35">
@@ -1444,19 +1444,19 @@
         <v>0.181357</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.07227</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.005132</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.009891</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.07908</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.33971</v>
       </c>
     </row>
     <row r="37">
@@ -1780,19 +1780,19 @@
         <v>0.002</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.205357</v>
+        <v>0.133087</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.054369</v>
+        <v>0.049237</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.030079</v>
+        <v>0.020188</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.08601300000000001</v>
+        <v>0.006933</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.807314</v>
+        <v>0.467604</v>
       </c>
     </row>
     <row r="49">
@@ -3976,16 +3976,16 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.038595</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.026539</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.040755</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.043057</v>
       </c>
     </row>
     <row r="125">
@@ -4004,16 +4004,16 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.038595</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.026539</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.040755</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.043057</v>
       </c>
     </row>
     <row r="126">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7861,7 +7861,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -10563,7 +10567,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -11173,7 +11177,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -11791,7 +11795,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">

--- a/output/pdf_financials_xlsx/MLO.xlsx
+++ b/output/pdf_financials_xlsx/MLO.xlsx
@@ -1213,13 +1213,13 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.002415</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.031566</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.028984</v>
@@ -1241,13 +1241,13 @@
         <v>-0.104496</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.747368</v>
+        <v>-0.744953</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-5.961436</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.5908949999999999</v>
+        <v>-0.559329</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.5809260000000001</v>
@@ -3301,13 +3301,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.002415</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.031566</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -8588,7 +8588,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -8947,7 +8951,11 @@
           <t>Depreciation – right of use asset</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MLO.xlsx
+++ b/output/pdf_financials_xlsx/MLO.xlsx
@@ -3609,10 +3609,10 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01135</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009263</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -4267,10 +4267,10 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01135</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009263</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -4295,10 +4295,10 @@
         <v>-0.071058</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.832377</v>
+        <v>-0.843727</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.375239</v>
+        <v>-0.384502</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.6239170000000001</v>
@@ -8745,7 +8745,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -9359,7 +9363,11 @@
           <t>Proceeds from share issuance (note 6)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
